--- a/MemberTemplate.xlsx
+++ b/MemberTemplate.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASCC\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB02D75-45A9-42DB-B133-43B00810F6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6CFD11-2A28-430F-B49A-CC3FB94331BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="First" sheetId="1" r:id="rId1"/>
-    <sheet name="Second" sheetId="2" r:id="rId2"/>
+    <sheet name="Setup" sheetId="3" r:id="rId1"/>
+    <sheet name="First" sheetId="1" r:id="rId2"/>
+    <sheet name="Second" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">First!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Second!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">First!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Second!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="69">
   <si>
     <t>ID</t>
   </si>
@@ -210,13 +211,40 @@
   </si>
   <si>
     <t>70 Murray St</t>
+  </si>
+  <si>
+    <t>SADC</t>
+  </si>
+  <si>
+    <t>Zip</t>
+  </si>
+  <si>
+    <t>Cars</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Emily Wu</t>
+  </si>
+  <si>
+    <t>Steven Bonnano</t>
+  </si>
+  <si>
+    <t>Steven Jordan</t>
+  </si>
+  <si>
+    <t>1072 80th St</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +255,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -247,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -255,11 +299,73 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -293,6 +399,18 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -572,6 +690,99 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF27723-B52E-4D71-B27A-CC03CEF15191}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="18"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="12">
+        <v>11228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="13">
+        <v>40.6201972</v>
+      </c>
+      <c r="B5" s="14">
+        <v>-74.015425500000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="18"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A7:B7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1067,7 +1278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E4A800-C376-4B9C-BDA9-DD2DF99A2191}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/MemberTemplate.xlsx
+++ b/MemberTemplate.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6CFD11-2A28-430F-B49A-CC3FB94331BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="3" r:id="rId1"/>

--- a/MemberTemplate.xlsx
+++ b/MemberTemplate.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6CFD11-2A28-430F-B49A-CC3FB94331BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="3" r:id="rId1"/>

--- a/MemberTemplate.xlsx
+++ b/MemberTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASCC\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6CFD11-2A28-430F-B49A-CC3FB94331BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682F8E12-1A31-4841-8A86-3639F5276138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10980" yWindow="390" windowWidth="17820" windowHeight="15090" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -238,6 +238,15 @@
   </si>
   <si>
     <t>1072 80th St</t>
+  </si>
+  <si>
+    <t>Staten Island</t>
+  </si>
+  <si>
+    <t>118 Cortelyou Ave</t>
+  </si>
+  <si>
+    <t>Shamrock Holmie</t>
   </si>
 </sst>
 </file>
@@ -365,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -384,10 +393,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -698,54 +703,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>11228</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>40.6201972</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>-74.015425500000006</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="18"/>
+      <c r="B7" s="17"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>64</v>
       </c>
     </row>
@@ -820,33 +825,33 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>26658</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>11219</v>
       </c>
       <c r="H2">
@@ -857,25 +862,25 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>23196</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>11223</v>
       </c>
       <c r="H3">
@@ -886,25 +891,25 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>20028</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>11232</v>
       </c>
       <c r="H4">
@@ -915,25 +920,25 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>29384</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>11220</v>
       </c>
       <c r="H5">
@@ -944,25 +949,25 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>27474</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>11225</v>
       </c>
       <c r="H6">
@@ -973,25 +978,25 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>33191</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>11216</v>
       </c>
       <c r="H7">
@@ -1002,25 +1007,25 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>31146</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>11203</v>
       </c>
       <c r="H8">
@@ -1031,25 +1036,25 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>34961</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>11236</v>
       </c>
       <c r="H9">
@@ -1060,25 +1065,25 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>26328</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>11234</v>
       </c>
       <c r="H10">
@@ -1089,25 +1094,25 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>32360</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>11208</v>
       </c>
       <c r="H11">
@@ -1118,25 +1123,25 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>25184</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>10012</v>
       </c>
       <c r="H12">
@@ -1147,25 +1152,25 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>33749</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <v>10014</v>
       </c>
       <c r="H13">
@@ -1176,25 +1181,25 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>30975</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="7">
         <v>10007</v>
       </c>
       <c r="H14">
@@ -1205,25 +1210,25 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>29315</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="7">
         <v>10002</v>
       </c>
       <c r="H15">
@@ -1234,25 +1239,25 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>33065</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <v>10002</v>
       </c>
       <c r="H16">
@@ -1262,14 +1267,34 @@
         <v>-73.982560899999996</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="8">
+        <v>32562</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="3">
+        <v>10312</v>
+      </c>
+      <c r="H17">
+        <v>40.55686</v>
+      </c>
+      <c r="I17">
+        <v>-74.164468200000002</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I16" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1316,10 +1341,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
     </row>

--- a/MemberTemplate.xlsx
+++ b/MemberTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASCC\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682F8E12-1A31-4841-8A86-3639F5276138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4090BEAB-39CD-4B06-94C0-EC4E6670AF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10980" yWindow="390" windowWidth="17820" windowHeight="15090" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10980" yWindow="390" windowWidth="17820" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>ID</t>
   </si>
@@ -247,6 +247,15 @@
   </si>
   <si>
     <t>Shamrock Holmie</t>
+  </si>
+  <si>
+    <t>Car #</t>
+  </si>
+  <si>
+    <t>ABC1234</t>
+  </si>
+  <si>
+    <t>NYC4567</t>
   </si>
 </sst>
 </file>
@@ -300,7 +309,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -370,11 +379,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -416,6 +440,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -696,19 +724,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF27723-B52E-4D71-B27A-CC03CEF15191}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
@@ -716,7 +744,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
@@ -724,7 +752,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>61</v>
       </c>
@@ -732,7 +760,7 @@
         <v>11228</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>40.6201972</v>
       </c>
@@ -740,48 +768,61 @@
         <v>-74.015425500000006</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="17"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="C8" s="15" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
         <v>65</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
         <v>66</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>6967</v>
+      </c>
+      <c r="B11" t="s">
         <v>67</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MemberTemplate.xlsx
+++ b/MemberTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASCC\Desktop\driverclusters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kai\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4090BEAB-39CD-4B06-94C0-EC4E6670AF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85879C5-D36F-412A-A5F8-044D6A1844A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10980" yWindow="390" windowWidth="17820" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="3" r:id="rId1"/>
@@ -434,6 +434,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -443,7 +444,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,10 +731,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -769,14 +769,14 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="16" t="s">
         <v>72</v>
       </c>
       <c r="B8" s="14" t="s">

--- a/MemberTemplate.xlsx
+++ b/MemberTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kai\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85879C5-D36F-412A-A5F8-044D6A1844A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DE4C68-07EC-42A2-9DF3-269CBC3DFD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
   <si>
     <t>ID</t>
   </si>
@@ -256,6 +256,12 @@
   </si>
   <si>
     <t>NYC4567</t>
+  </si>
+  <si>
+    <t>Tim Jarden</t>
+  </si>
+  <si>
+    <t>7524 11th Ave</t>
   </si>
 </sst>
 </file>
@@ -830,7 +836,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
@@ -1335,6 +1341,35 @@
       </c>
       <c r="I17">
         <v>-74.164468200000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="4">
+        <v>25316</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="3">
+        <v>11228</v>
+      </c>
+      <c r="H18">
+        <v>40.6225971</v>
+      </c>
+      <c r="I18">
+        <v>-74.012604699999997</v>
       </c>
     </row>
   </sheetData>

--- a/MemberTemplate.xlsx
+++ b/MemberTemplate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kai\Desktop\driverclusters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASCC\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DE4C68-07EC-42A2-9DF3-269CBC3DFD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14185A54-8CED-4AFA-AF3D-A9A42B899B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -84,24 +84,6 @@
     <t>New York</t>
   </si>
   <si>
-    <t>285 Fulton St</t>
-  </si>
-  <si>
-    <t>2532 86th St</t>
-  </si>
-  <si>
-    <t>1532 86th St</t>
-  </si>
-  <si>
-    <t>Johnny Smither</t>
-  </si>
-  <si>
-    <t>Johnnie Doer</t>
-  </si>
-  <si>
-    <t>Mary Ann Janer</t>
-  </si>
-  <si>
     <t>Alice Brown</t>
   </si>
   <si>
@@ -262,13 +244,112 @@
   </si>
   <si>
     <t>7524 11th Ave</t>
+  </si>
+  <si>
+    <t>Far SI</t>
+  </si>
+  <si>
+    <t>14-42 Opal Lane</t>
+  </si>
+  <si>
+    <t>49-1 Piedmont Ave</t>
+  </si>
+  <si>
+    <t>Close SI</t>
+  </si>
+  <si>
+    <t>206 W 100th St</t>
+  </si>
+  <si>
+    <t>Mid SI</t>
+  </si>
+  <si>
+    <t>314 Brookfield Ave</t>
+  </si>
+  <si>
+    <t>138 W 32nd St</t>
+  </si>
+  <si>
+    <t>Mid Man</t>
+  </si>
+  <si>
+    <t>135 Reade St</t>
+  </si>
+  <si>
+    <t>Low Man</t>
+  </si>
+  <si>
+    <t>Nort Man</t>
+  </si>
+  <si>
+    <t>134 Gatling Pl</t>
+  </si>
+  <si>
+    <t>Bay Ridge</t>
+  </si>
+  <si>
+    <t>Near Depot</t>
+  </si>
+  <si>
+    <t>Sunset</t>
+  </si>
+  <si>
+    <t>5604 8th Ave</t>
+  </si>
+  <si>
+    <t>325 State St</t>
+  </si>
+  <si>
+    <t>Atlantic</t>
+  </si>
+  <si>
+    <t>253 N 8th St</t>
+  </si>
+  <si>
+    <t>Willyburg</t>
+  </si>
+  <si>
+    <t>833 Sheffield Ave</t>
+  </si>
+  <si>
+    <t>NE BK</t>
+  </si>
+  <si>
+    <t>1962 E 37th St</t>
+  </si>
+  <si>
+    <t>E BK</t>
+  </si>
+  <si>
+    <t>E 26th St</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>69 Bay 40th St</t>
+  </si>
+  <si>
+    <t>Benny</t>
+  </si>
+  <si>
+    <t>376 Jefferson Ave</t>
+  </si>
+  <si>
+    <t>Stuy</t>
+  </si>
+  <si>
+    <t>Bath</t>
+  </si>
+  <si>
+    <t>1642 70th St</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +377,12 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -404,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -415,14 +502,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -441,6 +520,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -737,67 +819,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="18"/>
+      <c r="A1" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>68</v>
+      <c r="B2" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="11">
+      <c r="A4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="9">
         <v>11228</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>40.6201972</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>-74.015425500000006</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>64</v>
+      <c r="A8" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -805,10 +887,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -819,7 +901,7 @@
         <v>6967</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -872,33 +954,33 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>26658</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="5">
         <v>11219</v>
       </c>
       <c r="H2">
@@ -909,25 +991,25 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>23196</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="E3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5">
         <v>11223</v>
       </c>
       <c r="H3">
@@ -938,25 +1020,25 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>20028</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="E4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5">
         <v>11232</v>
       </c>
       <c r="H4">
@@ -967,25 +1049,25 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="8">
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6">
         <v>29384</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="D5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5">
         <v>11220</v>
       </c>
       <c r="H5">
@@ -996,25 +1078,25 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="6">
         <v>27474</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="D6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5">
         <v>11225</v>
       </c>
       <c r="H6">
@@ -1025,25 +1107,25 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6">
         <v>33191</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="E7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5">
         <v>11216</v>
       </c>
       <c r="H7">
@@ -1054,25 +1136,25 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6">
         <v>31146</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="D8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="5">
         <v>11203</v>
       </c>
       <c r="H8">
@@ -1083,25 +1165,25 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="8">
+      <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="6">
         <v>34961</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="7">
+      <c r="D9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5">
         <v>11236</v>
       </c>
       <c r="H9">
@@ -1112,25 +1194,25 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="8">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="6">
         <v>26328</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="7">
+      <c r="D10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5">
         <v>11234</v>
       </c>
       <c r="H10">
@@ -1141,25 +1223,25 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="8">
+      <c r="B11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="6">
         <v>32360</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="7">
+      <c r="D11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5">
         <v>11208</v>
       </c>
       <c r="H11">
@@ -1170,25 +1252,25 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="8">
+      <c r="B12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="6">
         <v>25184</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="7" t="s">
+      <c r="D12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <v>10012</v>
       </c>
       <c r="H12">
@@ -1199,25 +1281,25 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="6">
         <v>33749</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="D13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="5">
         <v>10014</v>
       </c>
       <c r="H13">
@@ -1228,25 +1310,25 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="8">
+      <c r="B14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="6">
         <v>30975</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="7" t="s">
+      <c r="D14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <v>10007</v>
       </c>
       <c r="H14">
@@ -1257,25 +1339,25 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="8">
+      <c r="B15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="6">
         <v>29315</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="7" t="s">
+      <c r="D15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="5">
         <v>10002</v>
       </c>
       <c r="H15">
@@ -1286,25 +1368,25 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="8">
+      <c r="B16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="6">
         <v>33065</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="7" t="s">
+      <c r="D16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <v>10002</v>
       </c>
       <c r="H16">
@@ -1319,19 +1401,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="8">
+        <v>65</v>
+      </c>
+      <c r="C17" s="6">
         <v>32562</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G17" s="3">
         <v>10312</v>
@@ -1348,7 +1430,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C18" s="4">
         <v>25316</v>
@@ -1357,7 +1439,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>12</v>
@@ -1381,10 +1463,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E4A800-C376-4B9C-BDA9-DD2DF99A2191}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -1396,7 +1478,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1417,10 +1499,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1429,28 +1511,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C2" s="4">
-        <v>26658</v>
+        <v>45292</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="6">
-        <v>10007</v>
+        <v>72</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="3">
+        <v>10309</v>
       </c>
       <c r="H2">
-        <v>40.712999199999999</v>
+        <v>40.524741900000002</v>
       </c>
       <c r="I2">
-        <v>-74.013189400000002</v>
+        <v>-74.215024900000003</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1458,28 +1540,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4">
-        <v>23196</v>
+        <v>45292</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="G3" s="3">
-        <v>11214</v>
+        <v>10305</v>
       </c>
       <c r="H3">
-        <v>40.597109600000003</v>
+        <v>40.602576399999997</v>
       </c>
       <c r="I3">
-        <v>-73.986383399999994</v>
+        <v>-74.074391300000002</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1487,32 +1569,439 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="C4" s="4">
-        <v>20028</v>
+        <v>45292</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="3">
+        <v>10308</v>
+      </c>
+      <c r="H4">
+        <v>40.559152099999999</v>
+      </c>
+      <c r="I4">
+        <v>-74.159261900000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3">
+        <v>10025</v>
+      </c>
+      <c r="H5">
+        <v>40.796718400000003</v>
+      </c>
+      <c r="I5">
+        <v>-73.969144200000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3">
+        <v>10001</v>
+      </c>
+      <c r="H6">
+        <v>40.748926599999997</v>
+      </c>
+      <c r="I6">
+        <v>-73.989927199999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3">
+        <v>10013</v>
+      </c>
+      <c r="H7">
+        <v>40.716227500000002</v>
+      </c>
+      <c r="I7">
+        <v>-74.009741099999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3">
+        <v>11209</v>
+      </c>
+      <c r="H8">
+        <v>40.617174800000001</v>
+      </c>
+      <c r="I8">
+        <v>-74.026383699999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3">
+        <v>11228</v>
+      </c>
+      <c r="H9">
+        <v>40.6225971</v>
+      </c>
+      <c r="I9">
+        <v>-74.012604699999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="3">
+        <v>11220</v>
+      </c>
+      <c r="H10">
+        <v>40.637762299999999</v>
+      </c>
+      <c r="I10">
+        <v>-74.007562199999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="3">
+        <v>11217</v>
+      </c>
+      <c r="H11">
+        <v>40.688287199999998</v>
+      </c>
+      <c r="I11">
+        <v>-73.985799299999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="3">
+        <v>11211</v>
+      </c>
+      <c r="H12">
+        <v>40.716361499999998</v>
+      </c>
+      <c r="I12">
+        <v>-73.953532100000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="3">
+        <v>11207</v>
+      </c>
+      <c r="H13">
+        <v>40.656318300000002</v>
+      </c>
+      <c r="I13">
+        <v>-73.889918899999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="3">
+        <v>11234</v>
+      </c>
+      <c r="H14">
+        <v>40.610578199999999</v>
+      </c>
+      <c r="I14">
+        <v>-73.931320799999995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3">
-        <v>11228</v>
-      </c>
-      <c r="H4">
-        <v>40.610622399999997</v>
-      </c>
-      <c r="I4">
-        <v>-74.008786999999998</v>
+      <c r="B15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="3">
+        <v>11229</v>
+      </c>
+      <c r="H15">
+        <v>40.621450299999999</v>
+      </c>
+      <c r="I15">
+        <v>-73.949726400000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="3">
+        <v>11214</v>
+      </c>
+      <c r="H16">
+        <v>40.596029600000001</v>
+      </c>
+      <c r="I16">
+        <v>-73.9876936</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3">
+        <v>11221</v>
+      </c>
+      <c r="H17">
+        <v>40.683928299999998</v>
+      </c>
+      <c r="I17">
+        <v>-73.942789399999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="4">
+        <v>45292</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="3">
+        <v>11204</v>
+      </c>
+      <c r="H18">
+        <v>40.618357000000003</v>
+      </c>
+      <c r="I18">
+        <v>-73.996957899999998</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{37E4A800-C376-4B9C-BDA9-DD2DF99A2191}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>